--- a/artfynd/A 19336-2024 artfynd.xlsx
+++ b/artfynd/A 19336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116633854</v>
+        <v>116633971</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510644</v>
+        <v>510612</v>
       </c>
       <c r="R2" t="n">
-        <v>6959551</v>
+        <v>6959477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116633839</v>
+        <v>116633854</v>
       </c>
       <c r="B3" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,27 +787,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510726</v>
+        <v>510644</v>
       </c>
       <c r="R3" t="n">
-        <v>6959517</v>
+        <v>6959551</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,17 +852,13 @@
           <t>2024-05-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Basalt hack på gran. Äldre</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116633765</v>
+        <v>116633866</v>
       </c>
       <c r="B4" t="n">
-        <v>90466</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511028</v>
+        <v>510616</v>
       </c>
       <c r="R4" t="n">
-        <v>6959272</v>
+        <v>6959480</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,42 +978,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116633799</v>
+        <v>116633839</v>
       </c>
       <c r="B5" t="n">
-        <v>90466</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510694</v>
+        <v>510726</v>
       </c>
       <c r="R5" t="n">
-        <v>6959440</v>
+        <v>6959517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,13 +1055,17 @@
           <t>2024-05-03</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Basalt hack på gran. Äldre</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,6 +1081,107 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>116633778</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fänån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>510924</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6959375</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Revsund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19336-2024 artfynd.xlsx
+++ b/artfynd/A 19336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633971</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633866</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633839</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116633778</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>